--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI Software Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OneOncology</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcbe2a6714229baf</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Data Lake, CI/CD, Git, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Databricks, PostgreSQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python/GenAI Solutions Architect (USA, Remote)</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL</t>
+          <t>RAG, S3, Glue, BigQuery, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba18b380fc57e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Applied Artificial Intelligence Scientist III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kubernetes, Terraform, Redshift, Kafka, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=a474c514b84ab2c5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kubernetes, Terraform, Redshift, Kafka, PostgreSQL, Python</t>
+          <t>Data Scientist, XGBoost, Docker, PySpark, Kafka, Hadoop, NoSQL, Tableau, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Pointwest Technologies Corp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kubernetes, Terraform, Redshift, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=13dcd4834939f146</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kubernetes, Terraform, Redshift, Kafka, PostgreSQL, Python</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8395d541fcdfbe00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Intermediate Quality Software Engineer</t>
+          <t>Sr Advanced AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R</t>
+          <t>LangChain, RAG, BigQuery, Data Lake, MLflow, FastAPI, Kubernetes, CI/CD, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559ccb02cb7d178f</t>
+          <t>https://www.indeed.com/viewjob?jk=b661df2c0cd9bcdb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunter Douglas</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Git, BigQuery, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3ef3957e1bb88d</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer (Research &amp; Development)</t>
+          <t>Fullstack Software Engineer, Notifications Lifecycle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git</t>
+          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, BigQuery, Kafka, PostgreSQL, Cassandra, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7005e3f4c4656a1</t>
+          <t>https://www.indeed.com/viewjob?jk=bda75d276ca12cb9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, BigQuery, BigQuery, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5688ac0e4584c89</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71f26e3ef313dd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist (Remote - US)</t>
+          <t>Software Engineer II, Lab Software</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f03078be278563</t>
+          <t>https://www.indeed.com/viewjob?jk=445da4a8f991b1a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Principle Engineer -In Bayesian, Large Foundational Systems, and Distributional Reinforcement Learning</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,46 +937,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1665a53cdb4a47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, CI/CD, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=65177bc64aa809f4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, PySpark, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=271606506b5aef8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer, TSG Infrastructure</t>
+          <t>Assistant Software Engineer - Autonomous Discovery Platforms (MADSCi)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d157b8182af574a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e75d35fc46dafc26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>WelbeHealth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6bd86a0d1851f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Snowflake, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=7c13278e1b33499f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, Snowflake, Databricks, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa680f752d2e1d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Sr. Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=68c3f22807d0f80a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Engineer-Bigdata &amp; Hadoop Engineer with Development experience</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=4e580193a9a810cd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (AI Solutions)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Coder</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, S3, FastAPI, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0c3d5c36e053d32</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4e0e0728ed01d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, US</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arize AI</t>
+          <t>Boot Barn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efece5d01689ce87</t>
+          <t>https://www.indeed.com/viewjob?jk=01e3a224717826ec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Design Automation Engineer - CRM</t>
+          <t>Senior Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, MLflow, Terraform, Snowflake, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a15845965d21de</t>
+          <t>https://www.indeed.com/viewjob?jk=de6fd71a91786e9c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior BI Front End Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Johnson Brothers</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,77 +1371,812 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2fafc7accbfc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e75d1beb4a1e483</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior BI Front End Developer</t>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Johnson Brothers</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ab15b873241878</t>
+          <t>https://www.indeed.com/viewjob?jk=68949396e4d3b02a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Workflow &amp; Systems Engineer, Operations</t>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Group1001</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=283a3e8c1a9a5140</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Solution Owner | AI &amp; Data Solutions</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39c38fa1eaf7a85</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd979e17bc56de92</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DevOps Engineering AMTS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7bb678559168699</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Data Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Five Below</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Snowflake, Databricks, PostgreSQL, MySQL, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, GenAI Data</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, S3, MLflow, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=590c0ba61cc10aa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Platform Engineer (AI/LLM Infrastructure)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e08c6cd812b19411</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Engineer - Stores &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74c71ba4424defd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Labcorp</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, MarTech Data Science and Measurement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Maleda Tech</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=247b13c0655dd72d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tech Faculty (Software Engineering &amp; Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Neumont College of Computer Science</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cba087c842520853</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Tableau, Quicksight, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bc6ed2cb62fe82</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbc12579adbfcb3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4524c00ef2a392e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, DevOps (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4ac6a29296c956</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend (Varying Levels)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Windfall</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, BigQuery, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f167bcc01670ae9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer -4 – Agentic AI &amp; Personalization</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a863e3048b6d0eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb43c2d163d026e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Snowflake, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a577c400c6df6d99</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data and AI Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, MySQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d8101ed42c40ec5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Senior Software Engineer, NYT Cooking</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=31ad8aa9682337b7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Search AI, BLAW/BTAX/BGOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Athena, Synapse, Data Lake, FastAPI, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1111256896b740e3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Health AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, MLflow, CI/CD, Jenkins, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f56543c1f2fdd111</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Redshift, Docker, Kubernetes, Terraform, Git, Redshift</t>
+          <t>RAG, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
+          <t>https://www.indeed.com/viewjob?jk=3dda6240b3e97c6a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lab Software</t>
+          <t>Senior Agentic Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55b20705bd64567</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a06efa71576cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Center Capacity Delivery</t>
+          <t>Senior Agentic Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f570fe201d7d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a530de06256bc27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ccdf02a39e8b18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Firefly Foundry</t>
+          <t>Senior Agentic Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1823d7d89d177e</t>
+          <t>https://www.indeed.com/viewjob?jk=43ea990a2b30c358</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, GenAI Data</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, S3, MLflow, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab4594d67eff100</t>
+          <t>https://www.indeed.com/viewjob?jk=0640118afc5bdfdb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EC2, Docker, Kubernetes, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d046847ba5f1ce93</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DevOps</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe82b890228d83a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbc8d21a5b56f7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DevOps (Cloud Operations Resilience Engineering)</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859fc308748876</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0c9c673261c16a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Revit .NET SDK Developer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Terraform, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,252 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b027cd6cf3fe51</t>
+          <t>https://www.indeed.com/viewjob?jk=202e791fdf3fd43e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Entry-level MuleSoft Junior Developer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f60b60fe2670a19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sparks, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ee3f9d0a47ab1a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb959620dfb61b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Escondido, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e72da67248c65db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Cloud DevOps Programmer Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84865c32fdd9bf64</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PySpark, Kafka, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Data &amp; Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Care Hospice</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0dae5c4651a07</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb2afffffa3b51a2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, NYT Cooking</t>
+          <t>Senior AI Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>9series</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Hugging Face, Pinecone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ad8aa9682337b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b370b79797c169f8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Search AI, BLAW/BTAX/BGOV</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1111256896b740e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, MLflow, CI/CD, Jenkins, Git, Databricks, PySpark</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56543c1f2fdd111</t>
+          <t>https://www.indeed.com/viewjob?jk=24286172101c9905</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dda6240b3e97c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=556ee20c38222d97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Agentic Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a06efa71576cc</t>
+          <t>https://www.indeed.com/viewjob?jk=00aa6b9c3711f9d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Agentic Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a530de06256bc27</t>
+          <t>https://www.indeed.com/viewjob?jk=303f3890589b8955</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ccdf02a39e8b18</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d1e06d3c159e59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Agentic Automation Engineer</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Docker, Kubernetes, Git, Python</t>
+          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ea990a2b30c358</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, MongoDB, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0640118afc5bdfdb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d046847ba5f1ce93</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbc8d21a5b56f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0c9c673261c16a</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202e791fdf3fd43e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60b60fe2670a19f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sparks, MD, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee3f9d0a47ab1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb959620dfb61b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Escondido, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72da67248c65db5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Programmer Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84865c32fdd9bf64</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PySpark, Kafka, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,322 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Data &amp; Integration Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Care Hospice</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, CI/CD, Git, BigQuery, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Omni-Channel Analytics Mgr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, BigQuery, Docker, Kubernetes, Git, Snowflake, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261396988b844ecd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7f8ded41b28903</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SOFT, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9665e7102eeb298a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW Platform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2afffffa3b51a2</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b745124a64a323f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, S3, EC2, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c319f49beb42a2a5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Full-Stack)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9series</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Hugging Face, Pinecone</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b370b79797c169f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GuidePoint Security</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Azure ML, S3, BigQuery, Synapse, Data Lake, MLflow, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24286172101c9905</t>
+          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>RAG, S3, Docker, AKS, CI/CD, Terraform, Git, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=556ee20c38222d97</t>
+          <t>https://www.indeed.com/viewjob?jk=fb587f45d8c72269</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist - AI Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>Data Scientist, RAG, TensorFlow, Kafka, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aa6b9c3711f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer (Research &amp; Development)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303f3890589b8955</t>
+          <t>https://www.indeed.com/viewjob?jk=52e9f75ca4efe0bf</t>
         </is>
       </c>
     </row>
@@ -683,20 +683,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d1e06d3c159e59</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1b7dc5e8daa63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevSecOps Platform Engineer, AI Automation</t>
+          <t>Software Development Engineer III - AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, CI/CD, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a5f8f556b11bd3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, MongoDB, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=ace41f2532791d23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f2730c7ab4aa6f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=c791fe17c24066c4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=22a124df8467d199</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Agentic/ Native AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f7c94504d615d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>Generative AI, Data Lake, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcc3a33c6fa276</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, FastAPI, Terraform, Git, Snowflake, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=560099b59a927b1c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=37a41baa3ffe1eb7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, Dataflow, Docker, CI/CD, Git, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arcade Food Theatre</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Dataflow, CI/CD, Git, BigQuery, Kafka, R</t>
+          <t>AI Engineer, LangChain, LLaMA, Gemini, AKS, Databricks, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=22839fac304897ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>First United Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DevOps Engineer &amp; Administrato</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Dataflow, FastAPI, CI/CD, BigQuery, Python, SQL</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,182 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Omni-Channel Analytics Mgr</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, BigQuery, Docker, Kubernetes, Git, Snowflake, BigQuery, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=261396988b844ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Skywalk Global</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f8ded41b28903</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SOFT, Inc.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9665e7102eeb298a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW Platform</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, AKS, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b745124a64a323f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, S3, EC2, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c319f49beb42a2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f86be0dbaa486401</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>OneOncology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, Azure ML, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
+          <t>https://www.indeed.com/viewjob?jk=2e920f1c0762bfce</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GuidePoint Security</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, BigQuery, Synapse, Data Lake, MLflow, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Hayden AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
+          <t>https://www.indeed.com/viewjob?jk=8737c0d3b9e71adf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Quantitative Geneticist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Ohalo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, AKS, CI/CD, Terraform, Git, MySQL, NoSQL, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, XGBoost, BigQuery, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb587f45d8c72269</t>
+          <t>https://www.indeed.com/viewjob?jk=03526299ce911d6d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Platform</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Kafka, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Git, Databricks, PySpark, Hadoop, Dask, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer (Research &amp; Development)</t>
+          <t>Forward Deployed AI Engineer – Claude 2026 - US</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git</t>
+          <t>AI Engineer, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e9f75ca4efe0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5717194645b638ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Solution Engineer (173209)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1b7dc5e8daa63</t>
+          <t>https://www.indeed.com/viewjob?jk=60d026abbf0c3ab9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer III - AI Engineer</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, CI/CD, Kafka, NoSQL, SQL</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a5f8f556b11bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d6869e05c1b7df4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, Kubernetes, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=368bfcb48411d0a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace41f2532791d23</t>
+          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f2730c7ab4aa6f</t>
+          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c791fe17c24066c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a124df8467d199</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agentic/ Native AI Engineer</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f7c94504d615d</t>
+          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, Data Lake, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcc3a33c6fa276</t>
+          <t>https://www.indeed.com/viewjob?jk=a641c5288812497c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI-ML Engineer - Finance-Hybrid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Keras, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8cefe3da829ff6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer - Applied AI</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Terraform, Git, Snowflake, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Copilot, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560099b59a927b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>RAG, Copilot, Dataflow, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a41baa3ffe1eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer ML Apps</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>PGW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Cheswick, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Docker, CI/CD, Git, Power BI, SQL, R, Scala</t>
+          <t>RAG, PyTorch, FastAPI, Docker, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
+          <t>https://www.indeed.com/viewjob?jk=5765a6aced8c5448</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arcade Food Theatre</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Gemini, AKS, Databricks, MongoDB, Python, R</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22839fac304897ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Innovation &amp; Systems Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Arc Building Partners</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f256632803e81312</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Quality Engineer - Safety Firmware</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>First United Bank</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer &amp; Administrato</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>S R International Inc</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f86be0dbaa486401</t>
+          <t>https://www.indeed.com/viewjob?jk=55e0dd49e6b34765</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-22.xlsx
+++ b/daily_matches/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI Software Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OneOncology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>Generative AI, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Kafka, Hadoop, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e920f1c0762bfce</t>
+          <t>https://www.indeed.com/viewjob?jk=e88a7bf9cdf22da2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL/Data Engineer</t>
+          <t>Software Engineer – Healthcare Systems &amp; Automation (On-Site Brooklyn, NY)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>True Care</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9f3b83186e48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hayden AI</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python</t>
+          <t>Data Scientist, RAG, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8737c0d3b9e71adf</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quantitative Geneticist</t>
+          <t>Senior Technical Consultant/ Solutions Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ohalo</t>
+          <t>Convr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, XGBoost, BigQuery, Git, BigQuery, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, MySQL, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03526299ce911d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=651407b70aa8891d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Git, Databricks, PySpark, Hadoop, Dask, Python</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=c14e4d10c6e22519</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer – Claude 2026 - US</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Git, Snowflake, Databricks, Python</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5717194645b638ad</t>
+          <t>https://www.indeed.com/viewjob?jk=afb67d72c9eae1bd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Solution Engineer (173209)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d026abbf0c3ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=578e74dac35a2574</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer &amp; Administrator</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d6869e05c1b7df4</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer, Developer Productivity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Glean Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368bfcb48411d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=df4854f9ec71d262</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Software Engineer, New College Grad - 2026, Foster City</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dd600e06d132b5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Software Engineer, New College Grad - 2026, Austin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
+          <t>https://www.indeed.com/viewjob?jk=9f95f509239629ec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc168f0fb266c5e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Senior Software Development Engineer - Agentic Search</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=edf50bf6c81614ed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>GEN AI PRODUCT OWNER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
+          <t>https://www.indeed.com/viewjob?jk=85c21dc245f3da84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Developer Advocate (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, S3, Glue, CI/CD, Git, Python, SQL</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a641c5288812497c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b31985a47c80e47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI-ML Engineer - Finance-Hybrid</t>
+          <t>Developer Advocate (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Keras, CI/CD, Git, Python</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8cefe3da829ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a7e75eb0b7d0c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Developer Advocate (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4836ca07b7d354</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Developer Advocate (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Dataflow, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=f97a37d11672d858</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer ML Apps</t>
+          <t>Advanced Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGW</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cheswick, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, FastAPI, Docker, Git, Python, SQL, R, Optimization</t>
+          <t>TensorFlow, PyTorch, OpenCV, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5765a6aced8c5448</t>
+          <t>https://www.indeed.com/viewjob?jk=b846f8606806cbd5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Senior AI Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Keras, Python, SQL, R, Julia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=257a9207e8a57acc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Innovation &amp; Systems Engineer</t>
+          <t>Software Engineer - AI Product Integration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arc Building Partners</t>
+          <t>Intapp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Git, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f256632803e81312</t>
+          <t>https://www.indeed.com/viewjob?jk=ceafb0f8b9dbf17b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quality Engineer - Safety Firmware</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>TensorFlow, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,287 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e0dd49e6b34765</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arkana Laboratories</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456a08b8dc4ee88e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Copilot, S3, Docker, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54b91e016da06d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e37dec326299e5d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Analyst, Applied AI Solutions</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51b3f8b84d37985e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Solutions Engineer (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39e13940ca951b1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Solutions Engineer (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab280d4d10675390</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Solutions Engineer (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0daa7e6f5715d5a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Solutions Engineer (Pre-Sales)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14c7912ce1bd2210</t>
         </is>
       </c>
     </row>
